--- a/VerveStacks_IDN_grids_kan/vt_vervestacks_IDN_v1.xlsx
+++ b/VerveStacks_IDN_grids_kan/vt_vervestacks_IDN_v1.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B5E1E19-31F2-47FB-9016-844CC55BE23E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{02A86831-485D-4EDF-9FD9-0493E2D386A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B1A075AE-D587-4996-9F61-D9D1F2F632B3}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E9F967DC-048E-492F-B9E7-011A9717484C}"/>
   </bookViews>
   <sheets>
     <sheet name="additional_hydro_pot" sheetId="5" r:id="rId1"/>
@@ -4670,7 +4670,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -4725,39 +4725,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -4809,7 +4809,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -4920,6 +4920,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -4928,13 +4935,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -4999,38 +4999,18 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C5877B3-B679-440D-ADDC-0C13B5C63A02}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF4F099F-026C-4D83-8AFC-858E99430D74}">
   <dimension ref="B9:O16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5335,7 +5315,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{448F2071-15DA-406F-8895-C7D73A6007C8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99E47A5A-AD7C-4257-9889-BB1AC2A5AAA8}">
   <dimension ref="B9:V257"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11470,7 +11450,7 @@
         <v>14</v>
       </c>
       <c r="R108" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="S108" t="s">
         <v>500</v>
@@ -11532,7 +11512,7 @@
         <v>14</v>
       </c>
       <c r="R109" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="S109" t="s">
         <v>500</v>
@@ -12338,7 +12318,7 @@
         <v>14</v>
       </c>
       <c r="R122" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="S122" t="s">
         <v>500</v>
@@ -12400,7 +12380,7 @@
         <v>14</v>
       </c>
       <c r="R123" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="S123" t="s">
         <v>500</v>
@@ -12834,7 +12814,7 @@
         <v>14</v>
       </c>
       <c r="R130" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="S130" t="s">
         <v>500</v>
@@ -12896,7 +12876,7 @@
         <v>14</v>
       </c>
       <c r="R131" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="S131" t="s">
         <v>500</v>
@@ -20549,7 +20529,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6604E9B-919A-4F3C-8BB8-7C991EA025EB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{614E5B25-09F9-4FB2-8F05-5737497F43C6}">
   <dimension ref="B9:V154"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -29206,7 +29186,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55A89587-854B-47E4-BB1D-D1975F92C897}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F33C0AD8-FDF7-4E62-85E2-6D870EF4DD2E}">
   <dimension ref="B9:V456"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -36463,7 +36443,7 @@
         <v>14</v>
       </c>
       <c r="R132" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S132" t="s">
         <v>500</v>
@@ -36522,7 +36502,7 @@
         <v>14</v>
       </c>
       <c r="R133" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="S133" t="s">
         <v>500</v>
@@ -36581,7 +36561,7 @@
         <v>14</v>
       </c>
       <c r="R134" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S134" t="s">
         <v>500</v>
@@ -36640,7 +36620,7 @@
         <v>14</v>
       </c>
       <c r="R135" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="S135" t="s">
         <v>500</v>
@@ -38029,10 +38009,10 @@
         <v>2024</v>
       </c>
       <c r="G159">
-        <v>0.23300000000000001</v>
+        <v>0.11700000000000001</v>
       </c>
       <c r="H159">
-        <v>0.32639999999999997</v>
+        <v>0.32640000000000002</v>
       </c>
       <c r="I159">
         <v>1610</v>
@@ -38088,10 +38068,10 @@
         <v>2024</v>
       </c>
       <c r="G160">
-        <v>0.11700000000000001</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="H160">
-        <v>0.32640000000000002</v>
+        <v>0.32639999999999997</v>
       </c>
       <c r="I160">
         <v>1610</v>
@@ -53905,7 +53885,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1748F374-C7B8-4912-9AC5-BD35D8C024AC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E0E6C08-223B-4354-AE85-E4BA30FA1AD3}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_IDN_grids_kan/vt_vervestacks_IDN_v1.xlsx
+++ b/VerveStacks_IDN_grids_kan/vt_vervestacks_IDN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{02A86831-485D-4EDF-9FD9-0493E2D386A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5AFDD4E8-D908-4C56-830E-075F876D6BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E9F967DC-048E-492F-B9E7-011A9717484C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B5362845-2F9C-43EA-9864-893EEDFDF81E}"/>
   </bookViews>
   <sheets>
     <sheet name="additional_hydro_pot" sheetId="5" r:id="rId1"/>
@@ -5010,7 +5010,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF4F099F-026C-4D83-8AFC-858E99430D74}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F36B303-0E8D-406E-9687-3D61FADC64BF}">
   <dimension ref="B9:O16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5315,7 +5315,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99E47A5A-AD7C-4257-9889-BB1AC2A5AAA8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69589921-018B-4994-9DB4-00E65C12165E}">
   <dimension ref="B9:V257"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11450,7 +11450,7 @@
         <v>14</v>
       </c>
       <c r="R108" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="S108" t="s">
         <v>500</v>
@@ -11512,7 +11512,7 @@
         <v>14</v>
       </c>
       <c r="R109" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="S109" t="s">
         <v>500</v>
@@ -12814,7 +12814,7 @@
         <v>14</v>
       </c>
       <c r="R130" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="S130" t="s">
         <v>500</v>
@@ -12876,7 +12876,7 @@
         <v>14</v>
       </c>
       <c r="R131" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="S131" t="s">
         <v>500</v>
@@ -20529,7 +20529,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{614E5B25-09F9-4FB2-8F05-5737497F43C6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F777FBD6-9D20-4928-897F-B04222BF336B}">
   <dimension ref="B9:V154"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -29186,7 +29186,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F33C0AD8-FDF7-4E62-85E2-6D870EF4DD2E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A2C8944-1B27-4306-ADF5-4E53325B9D9F}">
   <dimension ref="B9:V456"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -36207,7 +36207,7 @@
         <v>14</v>
       </c>
       <c r="R128" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S128" t="s">
         <v>500</v>
@@ -36266,7 +36266,7 @@
         <v>14</v>
       </c>
       <c r="R129" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="S129" t="s">
         <v>500</v>
@@ -53885,7 +53885,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E0E6C08-223B-4354-AE85-E4BA30FA1AD3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38F9CE84-132E-4037-BE7B-C168A70A264D}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
